--- a/docs/物料.xlsx
+++ b/docs/物料.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="50">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
   <si>
     <t>型号</t>
   </si>
@@ -179,6 +179,15 @@
   </si>
   <si>
     <t xml:space="preserve">https://e.tb.cn/h.ifROReE6ukEYHUw?tk=gkCxUCBdrNW </t>
+  </si>
+  <si>
+    <t>ov5647摄像头</t>
+  </si>
+  <si>
+    <t>csi摄像头，可直接插入树莓派专属接口</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://e.tb.cn/h.itYy4VFEoObBZ6t?tk=60o55jrPmxU </t>
   </si>
 </sst>
 </file>
@@ -884,13 +893,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="6">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyBorder="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1204,7 +1213,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:D17"/>
+  <dimension ref="A1:D25"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.4" outlineLevelCol="3"/>
   <cols>
     <col min="1" max="1" width="17.6666666666667" customWidth="1"/>
@@ -1425,7 +1434,7 @@
       <c r="C16" s="13" t="s">
         <v>45</v>
       </c>
-      <c r="D16" s="14" t="s">
+      <c r="D16" s="10" t="s">
         <v>46</v>
       </c>
     </row>
@@ -1439,9 +1448,65 @@
       <c r="C17" s="9">
         <v>1</v>
       </c>
-      <c r="D17" s="14" t="s">
+      <c r="D17" s="11" t="s">
         <v>49</v>
       </c>
+    </row>
+    <row r="18" spans="1:4">
+      <c r="A18" s="14" t="s">
+        <v>50</v>
+      </c>
+      <c r="B18" s="14" t="s">
+        <v>51</v>
+      </c>
+      <c r="C18" s="14">
+        <v>1</v>
+      </c>
+      <c r="D18" s="12" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="19" spans="1:4">
+      <c r="A19" s="14"/>
+      <c r="B19" s="14"/>
+      <c r="C19" s="14"/>
+      <c r="D19" s="14"/>
+    </row>
+    <row r="20" spans="1:4">
+      <c r="A20" s="14"/>
+      <c r="B20" s="14"/>
+      <c r="C20" s="14"/>
+      <c r="D20" s="14"/>
+    </row>
+    <row r="21" spans="1:4">
+      <c r="A21" s="14"/>
+      <c r="B21" s="14"/>
+      <c r="C21" s="14"/>
+      <c r="D21" s="14"/>
+    </row>
+    <row r="22" spans="1:4">
+      <c r="A22" s="14"/>
+      <c r="B22" s="14"/>
+      <c r="C22" s="14"/>
+      <c r="D22" s="14"/>
+    </row>
+    <row r="23" spans="1:4">
+      <c r="A23" s="14"/>
+      <c r="B23" s="14"/>
+      <c r="C23" s="14"/>
+      <c r="D23" s="14"/>
+    </row>
+    <row r="24" spans="1:4">
+      <c r="A24" s="14"/>
+      <c r="B24" s="14"/>
+      <c r="C24" s="14"/>
+      <c r="D24" s="14"/>
+    </row>
+    <row r="25" spans="1:4">
+      <c r="A25" s="14"/>
+      <c r="B25" s="14"/>
+      <c r="C25" s="14"/>
+      <c r="D25" s="14"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1466,6 +1531,7 @@
     <hyperlink ref="D13" r:id="rId13" display="https://e.tb.cn/h.iUOjkceT7srC8NA?tk=RMaWUCBZ5Fb"/>
     <hyperlink ref="D16" r:id="rId14" display="https://e.tb.cn/h.ifRjwoZ5adveDb8?tk=u7lHUCBYTl4"/>
     <hyperlink ref="D17" r:id="rId15" display="https://e.tb.cn/h.ifROReE6ukEYHUw?tk=gkCxUCBdrNW "/>
+    <hyperlink ref="D18" r:id="rId16" display="https://e.tb.cn/h.itYy4VFEoObBZ6t?tk=60o55jrPmxU "/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>

--- a/docs/物料.xlsx
+++ b/docs/物料.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="53">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="59" uniqueCount="59">
   <si>
     <t>型号</t>
   </si>
@@ -188,6 +188,24 @@
   </si>
   <si>
     <t xml:space="preserve">https://e.tb.cn/h.itYy4VFEoObBZ6t?tk=60o55jrPmxU </t>
+  </si>
+  <si>
+    <t>2D激光雷达</t>
+  </si>
+  <si>
+    <t>乐动D500 LD 19P 5000采样率，抗光干扰强</t>
+  </si>
+  <si>
+    <t>https://e.tb.cn/h.iGzF3tkndK87rkz?tk=ZNha5jtk7x9</t>
+  </si>
+  <si>
+    <t>9轴IMU模块</t>
+  </si>
+  <si>
+    <t>3轴加速度，3轴陀螺仪，3轴磁力计，USB串口</t>
+  </si>
+  <si>
+    <t xml:space="preserve">https://e.tb.cn/h.iGzHxmTPYkFiKhB?tk=n2DY5jt8rLJ </t>
   </si>
 </sst>
 </file>
@@ -359,7 +377,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="34">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -369,6 +387,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="4" tint="0.8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -732,7 +756,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="4">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="4">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0">
@@ -756,16 +780,16 @@
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="4" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="8">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="7">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="9">
+    <xf numFmtId="0" fontId="10" fillId="5" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="8">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="6" borderId="7">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="9">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="10">
@@ -774,85 +798,85 @@
     <xf numFmtId="0" fontId="15" fillId="0" borderId="11">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="8" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="9" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="10" borderId="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="11" borderId="0">
+    <xf numFmtId="0" fontId="16" fillId="8" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="9" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="11" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="12" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="13" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="13" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="14" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="15" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="15" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="16" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="17" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="17" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="18" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="19" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="19" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="20" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="22" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="23" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="23" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="24" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="25" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="25" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="26" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="27" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="28" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="29" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="29" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="30" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0">
+    <xf numFmtId="0" fontId="19" fillId="31" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="32" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="33" borderId="0">
+    <xf numFmtId="0" fontId="20" fillId="33" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="34" borderId="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -893,13 +917,13 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyBorder="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="6" applyBorder="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1392,7 +1416,7 @@
       <c r="C13" s="9">
         <v>1</v>
       </c>
-      <c r="D13" s="12" t="s">
+      <c r="D13" s="11" t="s">
         <v>36</v>
       </c>
     </row>
@@ -1431,7 +1455,7 @@
       <c r="B16" s="9" t="s">
         <v>44</v>
       </c>
-      <c r="C16" s="13" t="s">
+      <c r="C16" s="12" t="s">
         <v>45</v>
       </c>
       <c r="D16" s="10" t="s">
@@ -1453,60 +1477,76 @@
       </c>
     </row>
     <row r="18" spans="1:4">
-      <c r="A18" s="14" t="s">
+      <c r="A18" s="9" t="s">
         <v>50</v>
       </c>
-      <c r="B18" s="14" t="s">
+      <c r="B18" s="9" t="s">
         <v>51</v>
       </c>
-      <c r="C18" s="14">
+      <c r="C18" s="9">
         <v>1</v>
       </c>
-      <c r="D18" s="12" t="s">
+      <c r="D18" s="10" t="s">
         <v>52</v>
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="14"/>
-      <c r="B19" s="14"/>
-      <c r="C19" s="14"/>
-      <c r="D19" s="14"/>
+      <c r="A19" s="13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B19" s="9" t="s">
+        <v>54</v>
+      </c>
+      <c r="C19" s="9">
+        <v>1</v>
+      </c>
+      <c r="D19" s="14" t="s">
+        <v>55</v>
+      </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="14"/>
-      <c r="B20" s="14"/>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
+      <c r="A20" s="13" t="s">
+        <v>56</v>
+      </c>
+      <c r="B20" s="9" t="s">
+        <v>57</v>
+      </c>
+      <c r="C20" s="9">
+        <v>1</v>
+      </c>
+      <c r="D20" s="14" t="s">
+        <v>58</v>
+      </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="14"/>
-      <c r="B21" s="14"/>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
     </row>
     <row r="22" spans="1:4">
-      <c r="A22" s="14"/>
-      <c r="B22" s="14"/>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
     </row>
     <row r="23" spans="1:4">
-      <c r="A23" s="14"/>
-      <c r="B23" s="14"/>
-      <c r="C23" s="14"/>
-      <c r="D23" s="14"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
     </row>
     <row r="24" spans="1:4">
-      <c r="A24" s="14"/>
-      <c r="B24" s="14"/>
-      <c r="C24" s="14"/>
-      <c r="D24" s="14"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
     </row>
     <row r="25" spans="1:4">
-      <c r="A25" s="14"/>
-      <c r="B25" s="14"/>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
     </row>
   </sheetData>
   <mergeCells count="4">
@@ -1532,6 +1572,8 @@
     <hyperlink ref="D16" r:id="rId14" display="https://e.tb.cn/h.ifRjwoZ5adveDb8?tk=u7lHUCBYTl4"/>
     <hyperlink ref="D17" r:id="rId15" display="https://e.tb.cn/h.ifROReE6ukEYHUw?tk=gkCxUCBdrNW "/>
     <hyperlink ref="D18" r:id="rId16" display="https://e.tb.cn/h.itYy4VFEoObBZ6t?tk=60o55jrPmxU "/>
+    <hyperlink ref="D19" r:id="rId17" display="https://e.tb.cn/h.iGzF3tkndK87rkz?tk=ZNha5jtk7x9" tooltip="https://e.tb.cn/h.iGzF3tkndK87rkz?tk=ZNha5jtk7x9"/>
+    <hyperlink ref="D20" r:id="rId18" display="https://e.tb.cn/h.iGzHxmTPYkFiKhB?tk=n2DY5jt8rLJ "/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
